--- a/input/All_Chart_Information.xlsx
+++ b/input/All_Chart_Information.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hsa00\Desktop\OOB\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hsa00\Desktop\OOB\OS_Develop\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3767A5-46AD-4C6E-9682-85EA86D1F0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED598FB5-115F-47E1-8065-6CAB96B9284A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B0C6DF0-C161-4E1C-A452-B7238365BEB6}"/>
   </bookViews>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="4" spans="1:21" ht="12">
       <c r="A4" s="13">
-        <v>42213.67355324074</v>
+        <v>43991.592268518521</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>24</v>
